--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -732,19 +732,35 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>2</v>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -769,24 +785,24 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -798,7 +814,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1132,10 +1148,8 @@
           <t>Gan bdr Nepali</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9823540473</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9823540473</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1150,10 +1164,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9808567722</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9808567722</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1170,10 +1182,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.740481</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.740481</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1225,25 +1235,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,6</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.391452</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.391452</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1344,10 +1350,8 @@
           <t>Khem Moktan</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9849603796</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9849603796</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1362,10 +1366,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9849603796</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9849603796</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1382,10 +1384,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1441,53 +1441,261 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L55-1</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>23h 45m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>6m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>23h 45m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:20 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ON ROTER  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT ON ROTER</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377005</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Hariram Giri</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Hariram Giri</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9849146463</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:20:41 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9849146463H</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:42:57 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:20:41 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.73073</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Tusal Baluwatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L44-1</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.33402</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ON ROTER  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ON ROTER  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1556,10 +1556,8 @@
           <t>Hariram Giri</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9849146463</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9849146463</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1594,10 +1592,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.73073</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.73073</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1649,25 +1645,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L44-1</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33402</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33402</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT ON ROTER  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -808,7 +808,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1693,6 +1693,222 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374245</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Dura</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Dura</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9845791679</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:01:21 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9845791679</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:34:49 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:01:21 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.76114</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Budhanilkantha near Hello Kids Academy Montessori School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>sanamdura18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>12:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L16-4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.35745</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 26m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1760,10 +1760,8 @@
           <t>Sanam Dura</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9845791679</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9845791679</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1798,10 +1796,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.76114</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.76114</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1857,25 +1853,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L16-4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.35745</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.35745</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -562,18 +562,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -634,10 +652,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -657,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,6 +730,11 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -725,10 +749,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>3</v>
+      <c r="E2" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -743,7 +770,10 @@
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -757,10 +787,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>4</v>
+      <c r="E4" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -785,12 +818,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -804,11 +837,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="37" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -820,13 +853,13 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1898,6 +1931,430 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:25 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : renew with 444 speed unable to get qr code  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>renew with 444 speed unable to get qr code</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377568</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Min Somai</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Min Somai</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9840184511</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:25:52 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9840184511</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:19:05 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:25:52 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.738599</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>27.72743867591362, 85.29497190847236 GPS Coordinates Nearest: CDB275 (44m Road) Map: CG Balaju, Bagm</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>minsomai12345@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB276</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.310658</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : renew with 444 speed unable to get qr code  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>15h 6m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : renew with 444 speed unable to get qr code  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377066</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Accfin Business Management</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Accfin Business Management</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9818689989</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 10:15:48 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9818689989</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 10:15:48 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:43:36 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>27.727318 85.301878, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>accfinbusinessmanagement@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>09:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -580,18 +580,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -608,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -664,30 +682,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -702,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -730,10 +772,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -752,9 +799,12 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -773,27 +823,55 @@
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>6</v>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -807,13 +885,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -836,7 +914,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -848,7 +926,7 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -859,7 +937,7 @@
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2001,10 +2079,8 @@
           <t>Min Somai</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9840184511</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9840184511</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2039,10 +2115,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.738599</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.738599</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2098,25 +2172,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>CDB276</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.310658</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.310658</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : renew with 444 speed unable to get qr code  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2217,10 +2287,8 @@
           <t>Accfin Business Management</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9818689989</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9818689989</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2310,10 +2378,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2324,29 +2390,29 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 27m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 27m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2355,6 +2421,226 @@
       <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377099</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Sapkota</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Sapkota</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841509605</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:02 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841509605</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 10:52:07 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:02 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.672256</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Global Pathshala (Pre-school Block) M9FF+55J, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>pramodsapkota26@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>09:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.373051</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -546,14 +546,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -564,14 +564,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -598,18 +598,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -716,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -728,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -743,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -762,25 +781,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -793,19 +817,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>5</v>
+      <c r="G2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -815,10 +842,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -826,7 +853,10 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -843,12 +873,15 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -859,19 +892,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2491,10 +2527,8 @@
           <t>Pramod Sapkota</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2529,10 +2563,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.672256</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.672256</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2570,10 +2602,8 @@
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
@@ -2592,55 +2622,271 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.373051</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.373051</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 59m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377223</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Jinesh Shah</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Jinesh Shah</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9860601031</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:04:22 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9860601031A</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:27:17 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:04:22 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.685523</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur tenglafat, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>princethea1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>07:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.281078</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>1d 59m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 37m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -761,10 +761,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -826,32 +826,32 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -863,20 +863,20 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -886,28 +886,53 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>8</v>
+      <c r="G6" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -921,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -939,24 +964,24 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="37" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -970,7 +995,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -2737,10 +2762,8 @@
           <t>Jinesh Shah</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9860601031</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9860601031</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2775,10 +2798,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.685523</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.685523</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2816,10 +2837,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2838,55 +2857,667 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.281078</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.28107799999999</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 37m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:29 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376875</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Pratima Lama</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Pratima Lama</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9766368697</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:29:18 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>LTP9766368697</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 07:41:11 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:29:18 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>near by Toran Junior School - Preschool Bagdol Rd Lalitpur 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>9766368697@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>10:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB331</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>23h 37m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 48m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr">
+      <c r="AX10" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377973</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9861518467</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:34 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861518467</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:34 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:30:48 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinyak , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>9861518467@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>38m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>38m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:24 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377332</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Kumar Gubhaju</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Kumar Gubhaju</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9869666853</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:24:08 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9843692310</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:27:27 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:24:08 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near By Food Gallery - Family restaurant M9XM+PCM Kageshwori Manohara 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>05:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L55-4</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,32 +528,32 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -564,14 +564,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -582,54 +582,72 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>90.9%</t>
+      <c r="B8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -688,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -734,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -761,16 +779,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,30 +800,35 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -817,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -826,13 +850,16 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -851,12 +878,15 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -870,10 +900,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -881,7 +911,10 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -901,12 +934,15 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -917,22 +953,25 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -946,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -960,7 +999,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -976,7 +1015,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -986,7 +1025,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -995,7 +1034,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -2972,10 +3011,8 @@
           <t>Pratima Lama</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9766368697</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9766368697</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -3065,10 +3102,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -3079,7 +3114,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3180,10 +3215,8 @@
           <t>Bibek ghemasu</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9861518467</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9861518467</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3269,10 +3302,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3283,7 +3314,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3384,10 +3415,8 @@
           <t>Kumar Gubhaju</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9869666853</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9869666853</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3473,10 +3502,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -3487,37 +3514,1301 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : frequent disconnection  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377268</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Thing Tamang</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Thing Tamang</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9761610014</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:03:15 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9882051526</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:03:15 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.71026</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila miracle academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>bijaythingtamangz@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>06:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB338</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.27516</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>23h 43m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>23h 43m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377807</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Jakibanjar</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Jakibanjar</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9707517859</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:04:06 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9746292407</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:04:06 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.668988</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>MC9G+GGW, Mangal Ghat, Bhaktapur 44800, Near by ???? ?????? ????.??., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L30-7</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.42611</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>2h 37m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2h 37m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:38 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377006</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Aakriti Bhandari</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Aakriti Bhandari</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9847902722</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:38:21 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9847902722</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:46:06 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:38:21 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Maitidevi chowk , birendra marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>bhandaryaakriti9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>21h 56m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 52m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : frequent disconnection  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377020</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Ranju Nepali</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Ranju Nepali</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9813475180</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:37:48 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9880534715</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:04:28 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:37:48 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Glacier International School (school block) - Middle school M8QV+Q39 Thulo Kharibot Marga Kathmandu</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>ranjunepali432@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 33m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377918</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851160975</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:40:22 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9851160975</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:13:48 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:40:22 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.68498</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>near Holy Vision Technical Campus, M8MM+WV7, Sankhamul Marg, Kathmandu 44600, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>ideahub@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB154</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.33462</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi -6 router instal  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi -6 router instal</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377721</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Dhiraj Pyakurel</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Dhiraj Pyakurel</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841164298</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:38:07 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841164298</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:06:52 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:38:07 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.68136</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor kantipur guest house, arthasarokar, navjyoti college - -(-)-Lead, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>dhirajpyakurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB121</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.34809</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi -6 router instal  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi -6 router instal  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -968,10 +968,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1034,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="36" customWidth="1" min="47" max="47"/>
+    <col width="45" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -3615,10 +3615,8 @@
           <t>Bijay Thing Tamang</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9761610014</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9761610014</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3653,10 +3651,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.71026</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.71026</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3712,25 +3708,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB338</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.27516</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.27516</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3821,20 +3813,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Laxman Jakibanjar</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9707517859</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9707517859</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3869,10 +3855,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.668988</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.668988</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3920,25 +3904,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L30-7</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.42611</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.42610999999999</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -4039,10 +4019,8 @@
           <t>Aakriti Bhandari</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9847902722</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9847902722</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4132,10 +4110,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -4146,7 +4122,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4247,10 +4223,8 @@
           <t>Ranju Nepali</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9813475180</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9813475180</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4340,10 +4314,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -4354,7 +4326,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4455,10 +4427,8 @@
           <t>Idea Hub</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851160975</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851160975</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4493,10 +4463,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.68498</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.68498</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4548,25 +4516,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB154</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.33462</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.33462</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4667,10 +4631,8 @@
           <t>Dhiraj Pyakurel</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841164298</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841164298</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4705,10 +4667,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.68136</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.68136</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4760,55 +4720,699 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>CDB121</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.34809</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.34809</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi -6 router instal  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377409</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Sijapati</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Sijapati</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841055311</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:11:57 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9841055311</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:11:57 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:53:06 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.7165</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Near to Ganeshthan mandir,Kathmandu - Near to Ganeshthan mandir,Kathmandu, Kathmandu, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>sijapatiramesh07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>03:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.34217</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>20h 41m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>20h 41m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377409</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Sijapati</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Sijapati</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9841055311</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:11:57 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9841055311</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:11:57 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:53:06 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.7165</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Near to Ganeshthan mandir,Kathmandu - Near to Ganeshthan mandir,Kathmandu, Kathmandu, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>sijapatiramesh07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>03:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.34217</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>20h 41m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>20h 41m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:50 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377268</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Thing Tamang</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Thing Tamang</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9761610014</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:50:52 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9882051526</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:03:15 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:50:52 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.71026</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila miracle academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>bijaythingtamangz@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>06:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB338</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.27516</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>3h 31m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi -6 router instal  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -865,35 +865,35 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -903,13 +903,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2</v>
@@ -971,7 +971,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4835,10 +4835,8 @@
           <t>Ramesh Sijapati</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841055311</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841055311</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4873,10 +4871,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.7165</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.7165</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4932,25 +4928,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.34217</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.34217</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -5051,10 +5043,8 @@
           <t>Ramesh Sijapati</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9841055311</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9841055311</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5089,10 +5079,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.7165</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.7165</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -5148,25 +5136,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.34217</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.34217</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5267,10 +5251,8 @@
           <t>Bijay Thing Tamang</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9761610014</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9761610014</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5305,10 +5287,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.71026</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.71026</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5364,47 +5344,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB338</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.27516</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.27516</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>23h 47m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -5413,6 +5389,218 @@
       <c r="AX21" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 1:12 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>router damage</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377772</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Lamsal</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Lamsal</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9849645461</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:52:41 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9849645461</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:46:08 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:12:04 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.691409</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Easy Futsal old, M9R6+GRC, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>suryalamsal38@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Subash Sunuwar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L18-1</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.36226</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>3h 19m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 25m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -5449,20 +5449,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Surya Bahadur Lamsal</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9849645461</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9849645461</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5497,10 +5491,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.691409</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.691409</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5552,25 +5544,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L18-1</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.36226</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.36226000000001</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -844,13 +844,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -956,13 +956,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>4</v>
@@ -971,7 +971,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -5592,6 +5592,430 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 1:32 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377988</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Hanmant chavan</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Hanmant chavan</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9803182630</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:08:02 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9803182630</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:08:02 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:32:23 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.69839</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Ganeshman Singh Rd, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>rbajracharya2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.299</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 1:47 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377448</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Suman Lama</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Suman Lama</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9749720588</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:47:34 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9749720588</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 05:07:10 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:47:34 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.747671</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>P8X4+29J, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>02:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.305767</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>20h 40m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -5659,10 +5659,8 @@
           <t>Hanmant chavan</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9803182630</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9803182630</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5697,10 +5695,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.69839</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.69839</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5752,25 +5748,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.299</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.29900000000001</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5871,10 +5863,8 @@
           <t>Suman Lama</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9749720588</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9749720588</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5909,10 +5899,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.747671</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.747671</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5964,25 +5952,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L36-3</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.305767</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.305767</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -968,10 +968,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -6000,6 +6000,438 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377182</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Sajina Tamang</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Sajina Tamang</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841008479</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:48:06 AM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9841008479</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:48:06 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:03:05 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.71224</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>27.711110031636284, 85.28184822374293 GPS Coordinates Nearest: CDB258 (35m Road) Map: CG Sitapaila,</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>sajeenamoktan80@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>08:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB257</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.285503</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 14m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 14m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 2:02 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377182</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Sajina Tamang</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Sajina Tamang</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9841008479</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:48:06 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9841008479</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:48:06 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:03:05 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.71224</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>27.711110031636284, 85.28184822374293 GPS Coordinates Nearest: CDB258 (35m Road) Map: CG Sitapaila,</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>sajeenamoktan80@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>08:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>CDB257</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.285503</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 14m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 14m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -6067,10 +6067,8 @@
           <t>Sajina Tamang</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841008479</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841008479</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6105,10 +6103,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.71224</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.71224</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -6164,25 +6160,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB257</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.285503</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.28550300000001</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6283,10 +6275,8 @@
           <t>Sajina Tamang</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9841008479</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9841008479</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6321,10 +6311,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.71224</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.71224</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -6380,25 +6368,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>CDB257</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.285503</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.28550300000001</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -959,7 +959,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX26"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -6416,6 +6416,426 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 2:53 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378002</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Gopal lama</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Gopal lama</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851082831</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:53:28 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9851082831</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:21:44 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:53:28 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Police School - School P8M9+6FW ???????? ????? Kathmandu 44611, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>seasonalmp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L13-7</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 2:50 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377807</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Jakibanjar</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Jakibanjar</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9707517859</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:50:06 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9746292407</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:04:06 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:50:06 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.668988</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>MC9G+GGW, Mangal Ghat, Bhaktapur 44800, Near by ???? ?????? ????.??., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L30-7</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.42611</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>4h 46m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -6483,10 +6483,8 @@
           <t>Gopal lama</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851082831</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851082831</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6576,10 +6574,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -6590,7 +6586,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6681,20 +6677,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Laxman Jakibanjar</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9707517859</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9707517859</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6729,10 +6719,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.668988</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.668988</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6784,25 +6772,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>L30-7</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.42611</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.42610999999999</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -962,7 +962,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>4</v>
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -6820,6 +6820,226 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377885</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Adhiraki</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Adhiraki</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9849148651</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 03:23:45 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9849148651</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:50:41 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 03:23:45 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.74335</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Manmaiju,near Laligurans National Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>poudelprabhigya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.3141</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>4h 33m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -6887,10 +6887,8 @@
           <t>Jamuna Adhiraki</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9849148651</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9849148651</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6925,10 +6923,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.74335</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.74335</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6966,10 +6962,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
@@ -6988,25 +6982,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.3141</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.3141</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -956,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>4</v>
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -7030,6 +7030,210 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 3:52 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378059</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Upadhaya</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Upadhaya</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9841490562</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 03:52:30 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9841490562</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 03:52:30 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.696175, 85.29703, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB324</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -962,7 +962,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>4</v>
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7097,10 +7097,8 @@
           <t>Ramesh Upadhaya</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9841490562</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9841490562</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7186,10 +7184,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -7200,37 +7196,241 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377947</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Puspa Gurung</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Puspa Gurung</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9848768986</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:15:29 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9848768986</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:35:28 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:15:29 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>KTM CTY - Ganeshthan, Gongabu - Clothing store Ganeshthan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Mamata Bhujel</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L64-7</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>2h 15m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>4h 40m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW30" s="3" t="inlineStr">
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX30" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -881,13 +881,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -959,19 +959,19 @@
         <v>4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7297,10 +7297,8 @@
           <t>Puspa Gurung</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9848768986</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9848768986</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7386,10 +7384,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -7400,37 +7396,469 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>4h 40m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 4:30 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377848</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Khatiwada</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Khatiwada</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9865469922</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:30:42 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9865469922</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:27:54 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:30:42 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.71855</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Prithvinagar Bagmati Corridor Marga Narayantar, Jorpati,, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>sujan.khatiwada2022@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.3798</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>4h 40m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>6h 2m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW31" s="3" t="inlineStr">
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX31" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 4:27 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : router issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>router issue</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378130</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Debaki Shrestha</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Debaki Shrestha</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9841396463</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:27:36 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9841396463</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:40:09 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:27:36 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.672137</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Opp Mount SEBS School, Nareohate- 32, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>darshanshrestha56@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.351672</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : router issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : router issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -7497,10 +7497,8 @@
           <t>Sujan Khatiwada</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9865469922</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9865469922</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7535,10 +7533,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.71855</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.71855</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7594,25 +7590,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.3798</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.3798</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7713,10 +7705,8 @@
           <t>Debaki Shrestha</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9841396463</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9841396463</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7751,10 +7741,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.672137</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.672137</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7810,25 +7798,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.351672</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.35167199999999</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : router issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -921,14 +921,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -947,31 +947,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>28</v>
+      <c r="H7" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -7846,6 +7874,222 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377940</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9862297207</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:10:01 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9841168136</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:30:30 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:10:01 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.648692</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Nakhipot Basket Ball court,Bishal Chowk - Nakhipot Rd, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>yalung3695@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.317467</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>5h 39m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -993,13 +993,13 @@
         <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7941,10 +7941,8 @@
           <t>Badri Kuamar Rai</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9862297207</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9862297207</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7979,10 +7977,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.648692</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.648692</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -8038,55 +8034,483 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>3,7</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.317467</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.31746699999999</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>5h 39m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 5:32 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378153</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Balram Aryal</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Balram Aryal</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9841365755</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:32:14 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9841365755</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:57:58 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:32:14 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.670709</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Four Wheelers Auto Service Center,Sallaghari, Srijananagar, ??????? 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>kriti1155@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L21-1</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.404958</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>5h 39m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 5:27 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>router damage</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377772</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Lamsal</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Lamsal</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9849645461</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:27:53 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9849645461</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:46:08 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:27:53 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.691409</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Easy Futsal old, M9R6+GRC, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>suryalamsal38@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Subash Sunuwar</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>L18-1</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.36226</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>7h 41m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -990,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>6</v>
@@ -999,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8139,20 +8139,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="inlineStr">
         <is>
           <t>Balram Aryal</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9841365755</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9841365755</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -8187,10 +8181,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.670709</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.670709</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -8246,25 +8238,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L21-1</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.404958</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.40495799999999</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -8355,20 +8343,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="3" t="inlineStr">
         <is>
           <t>Surya Bahadur Lamsal</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9849645461</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9849645461</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8403,10 +8385,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.691409</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.691409</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -8462,55 +8442,267 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>L18-1</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.36226</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.36226000000001</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>7h 41m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : router damage   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 5:34 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378073</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Bhim pratap timilsina</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Bhim pratap timilsina</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9861000518</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:34:21 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9861000518</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:54:23 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:34:21 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.697949</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Hajurko Dhara, Ganesh Mandir M9XJ+C99, Kageshwori Manohara 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>nebia.prassanna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L53-1</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.380502</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>7h 41m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>3h 39m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : router damage   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW36" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_25_Oct_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -8557,10 +8557,8 @@
           <t>Bhim pratap timilsina</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9861000518</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9861000518</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8595,10 +8593,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.697949</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.697949</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -8654,25 +8650,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L53-1</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.380502</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.38050200000001</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
